--- a/files/excel-mastery-2-1-xlookup.xlsx
+++ b/files/excel-mastery-2-1-xlookup.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-1605" yWindow="-16320" windowWidth="29040" windowHeight="16440" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="280" windowWidth="17320" windowHeight="10400" tabRatio="773" firstSheet="2" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="2-1_実績集計_XLOOKUP" sheetId="1" state="visible" r:id="rId1"/>
@@ -553,7 +553,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="191">
+  <cellXfs count="192">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -1049,74 +1049,77 @@
     <xf numFmtId="3" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1604,88 +1607,88 @@
       <c r="D6" s="2" t="n"/>
     </row>
     <row r="7" ht="13.5" customHeight="1">
-      <c r="D7" s="171" t="inlineStr">
+      <c r="D7" s="168" t="inlineStr">
         <is>
           <t>行</t>
         </is>
       </c>
-      <c r="E7" s="171" t="inlineStr">
+      <c r="E7" s="168" t="inlineStr">
         <is>
           <t>B 商品コード</t>
         </is>
       </c>
-      <c r="F7" s="171" t="inlineStr">
+      <c r="F7" s="168" t="inlineStr">
         <is>
           <t>D 数量</t>
         </is>
       </c>
-      <c r="G7" s="171" t="inlineStr">
+      <c r="G7" s="168" t="inlineStr">
         <is>
           <t>F 売上(円)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="13.5" customHeight="1">
-      <c r="D8" s="172" t="n">
+      <c r="D8" s="169" t="n">
         <v>2</v>
       </c>
-      <c r="E8" s="172" t="inlineStr">
+      <c r="E8" s="169" t="inlineStr">
         <is>
           <t>F-102</t>
         </is>
       </c>
-      <c r="F8" s="172" t="n">
+      <c r="F8" s="169" t="n">
         <v>4</v>
       </c>
-      <c r="G8" s="173" t="n">
+      <c r="G8" s="170" t="n">
         <v>32000</v>
       </c>
     </row>
     <row r="9" ht="13.5" customHeight="1">
-      <c r="D9" s="172" t="n">
+      <c r="D9" s="169" t="n">
         <v>3</v>
       </c>
-      <c r="E9" s="172" t="inlineStr">
+      <c r="E9" s="169" t="inlineStr">
         <is>
           <t>F-101</t>
         </is>
       </c>
-      <c r="F9" s="172" t="n">
+      <c r="F9" s="169" t="n">
         <v>6</v>
       </c>
-      <c r="G9" s="173" t="n">
+      <c r="G9" s="170" t="n">
         <v>27000</v>
       </c>
     </row>
     <row r="10" ht="13.5" customHeight="1">
-      <c r="D10" s="172" t="n">
+      <c r="D10" s="169" t="n">
         <v>4</v>
       </c>
-      <c r="E10" s="172" t="inlineStr">
+      <c r="E10" s="169" t="inlineStr">
         <is>
           <t>F-103</t>
         </is>
       </c>
-      <c r="F10" s="172" t="n">
+      <c r="F10" s="169" t="n">
         <v>5</v>
       </c>
-      <c r="G10" s="173" t="n">
+      <c r="G10" s="170" t="n">
         <v>19000</v>
       </c>
     </row>
     <row r="11" ht="13.5" customHeight="1">
-      <c r="D11" s="172" t="n">
+      <c r="D11" s="169" t="n">
         <v>5</v>
       </c>
-      <c r="E11" s="172" t="inlineStr">
+      <c r="E11" s="169" t="inlineStr">
         <is>
           <t>F-999</t>
         </is>
       </c>
-      <c r="F11" s="172" t="n">
+      <c r="F11" s="169" t="n">
         <v>2</v>
       </c>
-      <c r="G11" s="173" t="n">
+      <c r="G11" s="170" t="n">
         <v>12000</v>
       </c>
     </row>
@@ -1731,12 +1734,12 @@
           <t>F-101</t>
         </is>
       </c>
-      <c r="E18" s="190" t="inlineStr">
+      <c r="E18" s="187" t="inlineStr">
         <is>
           <t>金目鯛煮付</t>
         </is>
       </c>
-      <c r="F18" s="190" t="n">
+      <c r="F18" s="187" t="n">
         <v>1800</v>
       </c>
     </row>
@@ -1746,12 +1749,12 @@
           <t>F-102</t>
         </is>
       </c>
-      <c r="E19" s="190" t="inlineStr">
+      <c r="E19" s="187" t="inlineStr">
         <is>
           <t>鮑ステーキ</t>
         </is>
       </c>
-      <c r="F19" s="190" t="n">
+      <c r="F19" s="187" t="n">
         <v>3200</v>
       </c>
     </row>
@@ -1761,12 +1764,12 @@
           <t>F-103</t>
         </is>
       </c>
-      <c r="E20" s="190" t="inlineStr">
+      <c r="E20" s="187" t="inlineStr">
         <is>
           <t>地魚刺身盛</t>
         </is>
       </c>
-      <c r="F20" s="190" t="n">
+      <c r="F20" s="187" t="n">
         <v>1500</v>
       </c>
     </row>
@@ -1833,32 +1836,32 @@
       <c r="D28" s="101" t="n">
         <v>2</v>
       </c>
-      <c r="E28" s="175" t="inlineStr">
+      <c r="E28" s="172" t="inlineStr">
         <is>
           <t>F-102</t>
         </is>
       </c>
-      <c r="F28" s="175">
+      <c r="F28" s="172">
         <f>_xlfn.XLOOKUP($E28,$D$17:$D$20,E$17:E$20,"該当なし")</f>
         <v/>
       </c>
-      <c r="G28" s="174">
+      <c r="G28" s="171">
         <f>SUMIFS($F$8:$F$11,$E$8:$E$11,E28)</f>
         <v/>
       </c>
-      <c r="H28" s="183">
+      <c r="H28" s="180">
         <f>_xlfn.XLOOKUP($E28,$D$17:$D$20,F$17:F$20,"該当なし")</f>
         <v/>
       </c>
-      <c r="I28" s="186">
+      <c r="I28" s="183">
         <f>IFERROR(G28*H28,"-")</f>
         <v/>
       </c>
-      <c r="J28" s="186">
+      <c r="J28" s="183">
         <f>SUMIFS($G$8:$G$11,$E$8:$E$11,E28)</f>
         <v/>
       </c>
-      <c r="K28" s="176">
+      <c r="K28" s="173">
         <f>IFERROR(I28/J28,"-")</f>
         <v/>
       </c>
@@ -1867,32 +1870,32 @@
       <c r="D29" s="104" t="n">
         <v>3</v>
       </c>
-      <c r="E29" s="178" t="inlineStr">
+      <c r="E29" s="175" t="inlineStr">
         <is>
           <t>F-101</t>
         </is>
       </c>
-      <c r="F29" s="178">
+      <c r="F29" s="175">
         <f>_xlfn.XLOOKUP($E29,$D$17:$D$20,E$17:E$20,"該当なし")</f>
         <v/>
       </c>
-      <c r="G29" s="177">
+      <c r="G29" s="174">
         <f>SUMIFS($F$8:$F$11,$E$8:$E$11,E29)</f>
         <v/>
       </c>
-      <c r="H29" s="184">
+      <c r="H29" s="181">
         <f>_xlfn.XLOOKUP($E29,$D$17:$D$20,F$17:F$20,"該当なし")</f>
         <v/>
       </c>
-      <c r="I29" s="187">
+      <c r="I29" s="184">
         <f>IFERROR(G29*H29,"-")</f>
         <v/>
       </c>
-      <c r="J29" s="187">
+      <c r="J29" s="184">
         <f>SUMIFS($G$8:$G$11,$E$8:$E$11,E29)</f>
         <v/>
       </c>
-      <c r="K29" s="179">
+      <c r="K29" s="176">
         <f>IFERROR(I29/J29,"-")</f>
         <v/>
       </c>
@@ -1901,66 +1904,66 @@
       <c r="D30" s="104" t="n">
         <v>4</v>
       </c>
-      <c r="E30" s="178" t="inlineStr">
+      <c r="E30" s="175" t="inlineStr">
         <is>
           <t>F-103</t>
         </is>
       </c>
-      <c r="F30" s="178">
+      <c r="F30" s="175">
         <f>_xlfn.XLOOKUP($E30,$D$17:$D$20,E$17:E$20,"該当なし")</f>
         <v/>
       </c>
-      <c r="G30" s="177">
+      <c r="G30" s="174">
         <f>SUMIFS($F$8:$F$11,$E$8:$E$11,E30)</f>
         <v/>
       </c>
-      <c r="H30" s="184">
+      <c r="H30" s="181">
         <f>_xlfn.XLOOKUP($E30,$D$17:$D$20,F$17:F$20,"該当なし")</f>
         <v/>
       </c>
-      <c r="I30" s="187">
+      <c r="I30" s="184">
         <f>IFERROR(G30*H30,"-")</f>
         <v/>
       </c>
-      <c r="J30" s="187">
+      <c r="J30" s="184">
         <f>SUMIFS($G$8:$G$11,$E$8:$E$11,E30)</f>
         <v/>
       </c>
-      <c r="K30" s="179">
+      <c r="K30" s="176">
         <f>IFERROR(I30/J30,"-")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="13.5" customHeight="1">
-      <c r="D31" s="170" t="n">
+      <c r="D31" s="167" t="n">
         <v>5</v>
       </c>
-      <c r="E31" s="181" t="inlineStr">
+      <c r="E31" s="178" t="inlineStr">
         <is>
           <t>F-999</t>
         </is>
       </c>
-      <c r="F31" s="181">
+      <c r="F31" s="178">
         <f>_xlfn.XLOOKUP($E31,$D$17:$D$20,E$17:E$20,"該当なし")</f>
         <v/>
       </c>
-      <c r="G31" s="180">
+      <c r="G31" s="177">
         <f>SUMIFS($F$8:$F$11,$E$8:$E$11,E31)</f>
         <v/>
       </c>
-      <c r="H31" s="185">
+      <c r="H31" s="182">
         <f>_xlfn.XLOOKUP($E31,$D$17:$D$20,F$17:F$20,"該当なし")</f>
         <v/>
       </c>
-      <c r="I31" s="188">
+      <c r="I31" s="185">
         <f>IFERROR(G31*H31,"-")</f>
         <v/>
       </c>
-      <c r="J31" s="188">
+      <c r="J31" s="185">
         <f>SUMIFS($G$8:$G$11,$E$8:$E$11,E31)</f>
         <v/>
       </c>
-      <c r="K31" s="182">
+      <c r="K31" s="179">
         <f>IFERROR(I31/J31,"-")</f>
         <v/>
       </c>
